--- a/data/trans_orig/IP16B02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B02-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22749</t>
+          <t>23178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>25552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>55538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78912</t>
+          <t>78049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24719</t>
+          <t>24795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>30814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29707</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37414</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>68961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121270</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35224</t>
+          <t>34889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>55696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49505</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>91907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103806</t>
+          <t>103862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
